--- a/月額_分割統合.xlsx
+++ b/月額_分割統合.xlsx
@@ -8,23 +8,31 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\offic\python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28269C5B-378B-4F00-85C9-15F3BB774E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D79205A-1352-48FD-A0D2-5072EB6BFDC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29445" yWindow="435" windowWidth="23205" windowHeight="14820" xr2:uid="{5AA50BA7-59BB-4F8D-9D40-E32F9614EBD2}"/>
+    <workbookView xWindow="2790" yWindow="1050" windowWidth="23895" windowHeight="13830" activeTab="6" xr2:uid="{5AA50BA7-59BB-4F8D-9D40-E32F9614EBD2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="5" r:id="rId4"/>
+    <sheet name="Sheet11" sheetId="8" r:id="rId2"/>
+    <sheet name="Sheet5" sheetId="7" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId4"/>
+    <sheet name="Sheet6" sheetId="9" r:id="rId5"/>
+    <sheet name="Sheet7" sheetId="10" r:id="rId6"/>
+    <sheet name="Sheet8" sheetId="11" r:id="rId7"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId8"/>
+    <sheet name="Sheet4" sheetId="5" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$1:$F$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Sheet2!$A$1:$F$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sheet6!$A$1:$G$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Sheet7!$A$1:$G$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Sheet8!$A$1:$G$113</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="146" r:id="rId5"/>
-    <pivotCache cacheId="152" r:id="rId6"/>
+    <pivotCache cacheId="291" r:id="rId10"/>
+    <pivotCache cacheId="292" r:id="rId11"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -41,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1676" uniqueCount="65">
   <si>
     <t>新 業務提携者（従属）</t>
   </si>
@@ -305,6 +313,28 @@
   </si>
   <si>
     <t>分割</t>
+  </si>
+  <si>
+    <t>タイプ1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>タイプ2</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>売上</t>
+    <rPh sb="0" eb="2">
+      <t>ウリアゲ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自社分</t>
+    <rPh sb="0" eb="3">
+      <t>ジシャブン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
   </si>
 </sst>
 </file>
@@ -671,7 +701,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -798,6 +828,21 @@
       </top>
       <bottom style="thin">
         <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -933,7 +978,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -964,7 +1009,16 @@
     <xf numFmtId="38" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1013,28 +1067,7 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="良い" xfId="7" builtinId="26" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFCCFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFCCFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFCCFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1056,7 +1089,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="keiri RES" refreshedDate="45695.753328125" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="14" xr:uid="{7AA76597-A2F5-454B-B128-7FB69478CB32}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="keiri RES" refreshedDate="45698.675154166667" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="14" xr:uid="{7AA76597-A2F5-454B-B128-7FB69478CB32}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:O15" sheet="Sheet1"/>
   </cacheSource>
@@ -1137,13 +1170,16 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="keiri RES" refreshedDate="45695.753368634258" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="112" xr:uid="{7920AFC6-E986-4518-B373-9916BF74D623}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="keiri RES" refreshedDate="45698.688698495367" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="112" xr:uid="{7920AFC6-E986-4518-B373-9916BF74D623}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:F113" sheet="Sheet2"/>
   </cacheSource>
   <cacheFields count="6">
     <cacheField name="タイプ" numFmtId="38">
-      <sharedItems/>
+      <sharedItems count="2">
+        <s v="月額"/>
+        <s v="分割"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="新 業務提携者（従属）" numFmtId="38">
       <sharedItems count="10">
@@ -1160,7 +1196,14 @@
       </sharedItems>
     </cacheField>
     <cacheField name="新 報酬率(自社)" numFmtId="38">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="30" maxValue="100"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="30" maxValue="100" count="6">
+        <n v="40"/>
+        <n v="45"/>
+        <n v="50"/>
+        <n v="60"/>
+        <n v="100"/>
+        <n v="30"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="自社報酬率" numFmtId="38">
       <sharedItems count="6">
@@ -1184,8 +1227,8 @@
         <s v="2025年5月(自)"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="合計金額" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="3781054"/>
+    <cacheField name="合計金額" numFmtId="38">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="3781054"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -1442,897 +1485,897 @@
 <file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="112">
   <r>
-    <s v="月額"/>
     <x v="0"/>
-    <n v="40"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <n v="118580"/>
   </r>
   <r>
-    <s v="月額"/>
     <x v="0"/>
-    <n v="40"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="1"/>
     <n v="47432"/>
   </r>
   <r>
-    <s v="月額"/>
     <x v="0"/>
-    <n v="40"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="2"/>
     <n v="118580"/>
   </r>
   <r>
-    <s v="月額"/>
     <x v="0"/>
-    <n v="40"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="3"/>
     <n v="47432"/>
   </r>
   <r>
-    <s v="月額"/>
     <x v="0"/>
-    <n v="40"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="4"/>
     <n v="118580"/>
   </r>
   <r>
-    <s v="月額"/>
     <x v="0"/>
-    <n v="40"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="5"/>
     <n v="47432"/>
   </r>
   <r>
-    <s v="月額"/>
     <x v="0"/>
-    <n v="40"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="6"/>
     <n v="118580"/>
   </r>
   <r>
-    <s v="月額"/>
     <x v="0"/>
-    <n v="40"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="7"/>
     <n v="47432"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="1"/>
-    <n v="45"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="0"/>
     <n v="2422035"/>
   </r>
   <r>
-    <s v="月額"/>
-    <x v="1"/>
-    <n v="45"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="1"/>
-    <n v="1089915.75"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1089858"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="1"/>
-    <n v="45"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="2"/>
     <n v="2422035"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="1"/>
-    <n v="45"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="3"/>
-    <n v="1089915.75"/>
+    <n v="1089858"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="1"/>
-    <n v="45"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="4"/>
     <n v="2422035"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="1"/>
-    <n v="45"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="5"/>
-    <n v="1089915.75"/>
+    <n v="1089858"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="1"/>
-    <n v="45"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="6"/>
     <n v="2422035"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="1"/>
-    <n v="45"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="7"/>
-    <n v="1089915.75"/>
+    <n v="1089858"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="1"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="0"/>
     <n v="1159450"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="1"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <n v="579725"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="1"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="2"/>
     <n v="1159450"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="1"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="3"/>
     <n v="579725"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="1"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="4"/>
     <n v="1159450"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="1"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="5"/>
     <n v="579725"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="1"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="6"/>
     <n v="1159450"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="1"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="7"/>
     <n v="579725"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="2"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="0"/>
     <n v="155370"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="2"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <n v="77685"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="2"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="2"/>
     <n v="155370"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="2"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="3"/>
     <n v="77685"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="2"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="4"/>
     <n v="155370"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="2"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="5"/>
     <n v="77685"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="2"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="6"/>
     <n v="155370"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="2"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="7"/>
     <n v="77685"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="3"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="0"/>
     <n v="27000"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="3"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <n v="13500"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="3"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="2"/>
     <n v="27000"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="3"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="3"/>
     <n v="13500"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="3"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="4"/>
     <n v="27000"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="3"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="5"/>
     <n v="13500"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="3"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="6"/>
     <n v="27000"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="3"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="7"/>
     <n v="13500"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="4"/>
-    <n v="60"/>
+    <x v="3"/>
     <x v="3"/>
     <x v="0"/>
     <n v="82500"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="4"/>
-    <n v="60"/>
+    <x v="3"/>
     <x v="3"/>
     <x v="1"/>
     <n v="49500"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="4"/>
-    <n v="60"/>
+    <x v="3"/>
     <x v="3"/>
     <x v="2"/>
     <n v="82500"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="4"/>
-    <n v="60"/>
+    <x v="3"/>
     <x v="3"/>
     <x v="3"/>
     <n v="49500"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="4"/>
-    <n v="60"/>
+    <x v="3"/>
     <x v="3"/>
     <x v="4"/>
     <n v="82500"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="4"/>
-    <n v="60"/>
+    <x v="3"/>
     <x v="3"/>
     <x v="5"/>
     <n v="49500"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="4"/>
-    <n v="60"/>
+    <x v="3"/>
     <x v="3"/>
     <x v="6"/>
     <n v="82500"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="4"/>
-    <n v="60"/>
+    <x v="3"/>
     <x v="3"/>
     <x v="7"/>
     <n v="49500"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="5"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="0"/>
     <n v="49000"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="5"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <n v="24500"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="5"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="2"/>
     <n v="49000"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="5"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="3"/>
     <n v="24500"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="5"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="4"/>
     <n v="49000"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="5"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="5"/>
     <n v="24500"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="5"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="6"/>
     <n v="49000"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="5"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="7"/>
     <n v="24500"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="6"/>
-    <n v="100"/>
+    <x v="4"/>
     <x v="4"/>
     <x v="0"/>
     <n v="106000"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="6"/>
-    <n v="100"/>
+    <x v="4"/>
     <x v="4"/>
     <x v="1"/>
     <n v="106000"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="6"/>
-    <n v="100"/>
+    <x v="4"/>
     <x v="4"/>
     <x v="2"/>
     <n v="106000"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="6"/>
-    <n v="100"/>
+    <x v="4"/>
     <x v="4"/>
     <x v="3"/>
     <n v="106000"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="6"/>
-    <n v="100"/>
+    <x v="4"/>
     <x v="4"/>
     <x v="4"/>
     <n v="106000"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="6"/>
-    <n v="100"/>
+    <x v="4"/>
     <x v="4"/>
     <x v="5"/>
     <n v="106000"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="6"/>
-    <n v="100"/>
+    <x v="4"/>
     <x v="4"/>
     <x v="6"/>
     <n v="106000"/>
   </r>
   <r>
-    <s v="月額"/>
+    <x v="0"/>
     <x v="6"/>
-    <n v="100"/>
+    <x v="4"/>
     <x v="4"/>
     <x v="7"/>
     <n v="106000"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="0"/>
     <x v="7"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="0"/>
     <n v="77000"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="0"/>
     <x v="7"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <n v="38500"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="0"/>
     <x v="7"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="2"/>
     <n v="77000"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="0"/>
     <x v="7"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="3"/>
     <n v="38500"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="0"/>
     <x v="7"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="4"/>
     <n v="77000"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="0"/>
     <x v="7"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="5"/>
     <n v="38500"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="0"/>
     <x v="7"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="6"/>
     <n v="77000"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="0"/>
     <x v="7"/>
-    <n v="50"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="7"/>
     <n v="38500"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="0"/>
-    <n v="40"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <n v="29100"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="0"/>
-    <n v="40"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="1"/>
     <n v="11640"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="0"/>
-    <n v="40"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="2"/>
     <n v="29100"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="0"/>
-    <n v="40"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="3"/>
     <n v="11640"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="0"/>
-    <n v="40"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="4"/>
     <n v="29100"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="0"/>
-    <n v="40"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="5"/>
     <n v="11640"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="0"/>
-    <n v="40"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="6"/>
     <n v="29100"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="0"/>
-    <n v="40"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="7"/>
     <n v="11640"/>
   </r>
   <r>
-    <s v="分割"/>
     <x v="1"/>
-    <n v="50"/>
+    <x v="1"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="0"/>
     <n v="3781054"/>
   </r>
   <r>
-    <s v="分割"/>
     <x v="1"/>
-    <n v="50"/>
+    <x v="1"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <n v="1890527"/>
   </r>
   <r>
-    <s v="分割"/>
     <x v="1"/>
-    <n v="50"/>
+    <x v="1"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="2"/>
     <n v="3576300"/>
   </r>
   <r>
-    <s v="分割"/>
     <x v="1"/>
-    <n v="50"/>
+    <x v="1"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="3"/>
     <n v="1788150"/>
   </r>
   <r>
-    <s v="分割"/>
     <x v="1"/>
-    <n v="50"/>
+    <x v="1"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="4"/>
     <n v="0"/>
   </r>
   <r>
-    <s v="分割"/>
     <x v="1"/>
-    <n v="50"/>
+    <x v="1"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="5"/>
     <n v="0"/>
   </r>
   <r>
-    <s v="分割"/>
     <x v="1"/>
-    <n v="50"/>
+    <x v="1"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="6"/>
     <n v="0"/>
   </r>
   <r>
-    <s v="分割"/>
     <x v="1"/>
-    <n v="50"/>
+    <x v="1"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="7"/>
     <n v="0"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="8"/>
-    <n v="30"/>
+    <x v="5"/>
     <x v="5"/>
     <x v="0"/>
     <n v="0"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="8"/>
-    <n v="30"/>
+    <x v="5"/>
     <x v="5"/>
     <x v="1"/>
     <n v="0"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="8"/>
-    <n v="30"/>
+    <x v="5"/>
     <x v="5"/>
     <x v="2"/>
     <n v="0"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="8"/>
-    <n v="30"/>
+    <x v="5"/>
     <x v="5"/>
     <x v="3"/>
     <n v="0"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="8"/>
-    <n v="30"/>
+    <x v="5"/>
     <x v="5"/>
     <x v="4"/>
     <n v="0"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="8"/>
-    <n v="30"/>
+    <x v="5"/>
     <x v="5"/>
     <x v="5"/>
     <n v="0"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="8"/>
-    <n v="30"/>
+    <x v="5"/>
     <x v="5"/>
     <x v="6"/>
     <n v="0"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="8"/>
-    <n v="30"/>
+    <x v="5"/>
     <x v="5"/>
     <x v="7"/>
     <n v="0"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="9"/>
-    <n v="60"/>
+    <x v="3"/>
     <x v="3"/>
     <x v="0"/>
     <n v="758940"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="9"/>
-    <n v="60"/>
+    <x v="3"/>
     <x v="3"/>
     <x v="1"/>
     <n v="455364"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="9"/>
-    <n v="60"/>
+    <x v="3"/>
     <x v="3"/>
     <x v="2"/>
     <n v="509940"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="9"/>
-    <n v="60"/>
+    <x v="3"/>
     <x v="3"/>
     <x v="3"/>
     <n v="305964"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="9"/>
-    <n v="60"/>
+    <x v="3"/>
     <x v="3"/>
     <x v="4"/>
     <n v="509940"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="9"/>
-    <n v="60"/>
+    <x v="3"/>
     <x v="3"/>
     <x v="5"/>
     <n v="305964"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="9"/>
-    <n v="60"/>
+    <x v="3"/>
     <x v="3"/>
     <x v="6"/>
     <n v="0"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="9"/>
-    <n v="60"/>
+    <x v="3"/>
     <x v="3"/>
     <x v="7"/>
     <n v="0"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="6"/>
-    <n v="100"/>
+    <x v="4"/>
     <x v="4"/>
     <x v="0"/>
     <n v="79500"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="6"/>
-    <n v="100"/>
+    <x v="4"/>
     <x v="4"/>
     <x v="1"/>
     <n v="79500"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="6"/>
-    <n v="100"/>
+    <x v="4"/>
     <x v="4"/>
     <x v="2"/>
     <n v="27500"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="6"/>
-    <n v="100"/>
+    <x v="4"/>
     <x v="4"/>
     <x v="3"/>
     <n v="27500"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="6"/>
-    <n v="100"/>
+    <x v="4"/>
     <x v="4"/>
     <x v="4"/>
     <n v="27500"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="6"/>
-    <n v="100"/>
+    <x v="4"/>
     <x v="4"/>
     <x v="5"/>
     <n v="27500"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="6"/>
-    <n v="100"/>
+    <x v="4"/>
     <x v="4"/>
     <x v="6"/>
     <n v="27500"/>
   </r>
   <r>
-    <s v="分割"/>
+    <x v="1"/>
     <x v="6"/>
-    <n v="100"/>
+    <x v="4"/>
     <x v="4"/>
     <x v="7"/>
     <n v="27500"/>
@@ -2341,7 +2384,225 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3095766F-7AF7-457F-8459-66329CC6A98E}" name="ピボットテーブル10" cacheId="152" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="値" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{58923439-4944-4F8E-A20F-189C571C2D3C}" name="ピボットテーブル17" cacheId="292" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="値" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A3:M19" firstHeaderRow="1" firstDataRow="2" firstDataCol="4"/>
+  <pivotFields count="6">
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="2">
+        <item x="0"/>
+        <item x="1"/>
+      </items>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="10">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="8"/>
+        <item x="4"/>
+        <item x="9"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+      </items>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" numFmtId="38" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="6">
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+      </items>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+      </items>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField axis="axisCol" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="8">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+      </items>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField dataField="1" compact="0" numFmtId="38" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="4">
+    <field x="0"/>
+    <field x="1"/>
+    <field x="2"/>
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="15">
+    <i>
+      <x/>
+      <x/>
+      <x v="1"/>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+      <x v="2"/>
+      <x v="3"/>
+    </i>
+    <i r="2">
+      <x v="3"/>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+      <x v="3"/>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+      <x v="3"/>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+      <x v="4"/>
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+      <x v="3"/>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+      <x v="5"/>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+      <x v="3"/>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="1"/>
+      <x/>
+      <x v="1"/>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+      <x v="3"/>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+      <x/>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+      <x v="4"/>
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+      <x v="5"/>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="4"/>
+  </colFields>
+  <colItems count="9">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="合計 / 合計金額" fld="5" baseField="0" baseItem="0" numFmtId="38"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" fillDownLabelsDefault="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3095766F-7AF7-457F-8459-66329CC6A98E}" name="ピボットテーブル10" cacheId="292" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="値" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:K16" firstHeaderRow="1" firstDataRow="2" firstDataCol="2"/>
   <pivotFields count="6">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -2483,8 +2744,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3A499D84-3EC2-4DB5-B267-4615C216EDD7}" name="ピボットテーブル11" cacheId="146" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="値" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3A499D84-3EC2-4DB5-B267-4615C216EDD7}" name="ピボットテーブル11" cacheId="291" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="値" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:M18" firstHeaderRow="0" firstDataRow="1" firstDataCol="3"/>
   <pivotFields count="15">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -2738,7 +2999,7 @@
     <dataField name="合計 / 2025年5月(自)" fld="14" baseField="0" baseItem="0" numFmtId="38"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="3">
+    <format dxfId="0">
       <pivotArea outline="0" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -3059,13 +3320,838 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41D7CBC0-7E43-4F4B-85F4-286B7D2A4518}">
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="23.125" customWidth="1"/>
     <col min="3" max="3" width="7.25" customWidth="1"/>
-    <col min="4" max="4" width="6" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="14.75" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="14.25" customWidth="1"/>
+    <col min="10" max="11" width="16" customWidth="1"/>
+    <col min="12" max="13" width="16.5" customWidth="1"/>
+    <col min="14" max="14" width="16.75" customWidth="1"/>
+    <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A1" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A2" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="10">
+        <v>40</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="10">
+        <v>664048</v>
+      </c>
+      <c r="F2" s="13">
+        <v>118580</v>
+      </c>
+      <c r="G2" s="13">
+        <v>47432</v>
+      </c>
+      <c r="H2" s="10">
+        <v>118580</v>
+      </c>
+      <c r="I2" s="10">
+        <v>47432</v>
+      </c>
+      <c r="J2" s="10">
+        <v>118580</v>
+      </c>
+      <c r="K2" s="10">
+        <v>47432</v>
+      </c>
+      <c r="L2" s="10">
+        <v>118580</v>
+      </c>
+      <c r="M2" s="10">
+        <v>47432</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A3" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="10">
+        <v>45</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="10">
+        <v>14047572</v>
+      </c>
+      <c r="F3" s="13">
+        <v>2422035</v>
+      </c>
+      <c r="G3" s="13">
+        <v>1089858</v>
+      </c>
+      <c r="H3" s="10">
+        <v>2422035</v>
+      </c>
+      <c r="I3" s="10">
+        <v>1089858</v>
+      </c>
+      <c r="J3" s="10">
+        <v>2422035</v>
+      </c>
+      <c r="K3" s="10">
+        <v>1089858</v>
+      </c>
+      <c r="L3" s="10">
+        <v>2422035</v>
+      </c>
+      <c r="M3" s="10">
+        <v>1089858</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A4" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="10">
+        <v>50</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="10">
+        <v>6956700</v>
+      </c>
+      <c r="F4" s="13">
+        <v>1159450</v>
+      </c>
+      <c r="G4" s="13">
+        <v>579725</v>
+      </c>
+      <c r="H4" s="10">
+        <v>1159450</v>
+      </c>
+      <c r="I4" s="10">
+        <v>579725</v>
+      </c>
+      <c r="J4" s="10">
+        <v>1159450</v>
+      </c>
+      <c r="K4" s="10">
+        <v>579725</v>
+      </c>
+      <c r="L4" s="10">
+        <v>1159450</v>
+      </c>
+      <c r="M4" s="10">
+        <v>579725</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="10">
+        <v>50</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="10">
+        <v>932220</v>
+      </c>
+      <c r="F5" s="13">
+        <v>155370</v>
+      </c>
+      <c r="G5" s="13">
+        <v>77685</v>
+      </c>
+      <c r="H5" s="10">
+        <v>155370</v>
+      </c>
+      <c r="I5" s="10">
+        <v>77685</v>
+      </c>
+      <c r="J5" s="10">
+        <v>155370</v>
+      </c>
+      <c r="K5" s="10">
+        <v>77685</v>
+      </c>
+      <c r="L5" s="10">
+        <v>155370</v>
+      </c>
+      <c r="M5" s="10">
+        <v>77685</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A6" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="10">
+        <v>50</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="10">
+        <v>162000</v>
+      </c>
+      <c r="F6" s="13">
+        <v>27000</v>
+      </c>
+      <c r="G6" s="13">
+        <v>13500</v>
+      </c>
+      <c r="H6" s="10">
+        <v>27000</v>
+      </c>
+      <c r="I6" s="10">
+        <v>13500</v>
+      </c>
+      <c r="J6" s="10">
+        <v>27000</v>
+      </c>
+      <c r="K6" s="10">
+        <v>13500</v>
+      </c>
+      <c r="L6" s="10">
+        <v>27000</v>
+      </c>
+      <c r="M6" s="10">
+        <v>13500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A7" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="10">
+        <v>60</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="10">
+        <v>528000</v>
+      </c>
+      <c r="F7" s="13">
+        <v>82500</v>
+      </c>
+      <c r="G7" s="13">
+        <v>49500</v>
+      </c>
+      <c r="H7" s="10">
+        <v>82500</v>
+      </c>
+      <c r="I7" s="10">
+        <v>49500</v>
+      </c>
+      <c r="J7" s="10">
+        <v>82500</v>
+      </c>
+      <c r="K7" s="10">
+        <v>49500</v>
+      </c>
+      <c r="L7" s="10">
+        <v>82500</v>
+      </c>
+      <c r="M7" s="10">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A8" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="10">
+        <v>50</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="10">
+        <v>294000</v>
+      </c>
+      <c r="F8" s="13">
+        <v>49000</v>
+      </c>
+      <c r="G8" s="13">
+        <v>24500</v>
+      </c>
+      <c r="H8" s="10">
+        <v>49000</v>
+      </c>
+      <c r="I8" s="10">
+        <v>24500</v>
+      </c>
+      <c r="J8" s="10">
+        <v>49000</v>
+      </c>
+      <c r="K8" s="10">
+        <v>24500</v>
+      </c>
+      <c r="L8" s="10">
+        <v>49000</v>
+      </c>
+      <c r="M8" s="10">
+        <v>24500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A9" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="10">
+        <v>100</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="10">
+        <v>848000</v>
+      </c>
+      <c r="F9" s="13">
+        <v>106000</v>
+      </c>
+      <c r="G9" s="13">
+        <v>106000</v>
+      </c>
+      <c r="H9" s="10">
+        <v>106000</v>
+      </c>
+      <c r="I9" s="10">
+        <v>106000</v>
+      </c>
+      <c r="J9" s="10">
+        <v>106000</v>
+      </c>
+      <c r="K9" s="10">
+        <v>106000</v>
+      </c>
+      <c r="L9" s="10">
+        <v>106000</v>
+      </c>
+      <c r="M9" s="10">
+        <v>106000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A10" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="10">
+        <v>50</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="10">
+        <v>462000</v>
+      </c>
+      <c r="F10" s="13">
+        <v>77000</v>
+      </c>
+      <c r="G10" s="13">
+        <v>38500</v>
+      </c>
+      <c r="H10" s="10">
+        <v>77000</v>
+      </c>
+      <c r="I10" s="10">
+        <v>38500</v>
+      </c>
+      <c r="J10" s="10">
+        <v>77000</v>
+      </c>
+      <c r="K10" s="10">
+        <v>38500</v>
+      </c>
+      <c r="L10" s="10">
+        <v>77000</v>
+      </c>
+      <c r="M10" s="10">
+        <v>38500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="10">
+        <v>40</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="10">
+        <v>162960</v>
+      </c>
+      <c r="F11" s="13">
+        <v>29100</v>
+      </c>
+      <c r="G11" s="13">
+        <v>11640</v>
+      </c>
+      <c r="H11" s="10">
+        <v>29100</v>
+      </c>
+      <c r="I11" s="10">
+        <v>11640</v>
+      </c>
+      <c r="J11" s="10">
+        <v>29100</v>
+      </c>
+      <c r="K11" s="10">
+        <v>11640</v>
+      </c>
+      <c r="L11" s="10">
+        <v>29100</v>
+      </c>
+      <c r="M11" s="10">
+        <v>11640</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A12" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="10">
+        <v>50</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="10">
+        <v>11036031</v>
+      </c>
+      <c r="F12" s="13">
+        <v>3781054</v>
+      </c>
+      <c r="G12" s="13">
+        <v>1890527</v>
+      </c>
+      <c r="H12" s="10">
+        <v>3576300</v>
+      </c>
+      <c r="I12" s="10">
+        <v>1788150</v>
+      </c>
+      <c r="J12" s="10">
+        <v>0</v>
+      </c>
+      <c r="K12" s="10">
+        <v>0</v>
+      </c>
+      <c r="L12" s="10">
+        <v>0</v>
+      </c>
+      <c r="M12" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A13" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="10">
+        <v>30</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="10">
+        <v>0</v>
+      </c>
+      <c r="F13" s="13">
+        <v>0</v>
+      </c>
+      <c r="G13" s="13">
+        <v>0</v>
+      </c>
+      <c r="H13" s="10">
+        <v>0</v>
+      </c>
+      <c r="I13" s="10">
+        <v>0</v>
+      </c>
+      <c r="J13" s="10">
+        <v>0</v>
+      </c>
+      <c r="K13" s="10">
+        <v>0</v>
+      </c>
+      <c r="L13" s="10">
+        <v>0</v>
+      </c>
+      <c r="M13" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A14" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="13">
+        <v>60</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="13">
+        <v>2846112</v>
+      </c>
+      <c r="F14" s="13">
+        <v>758940</v>
+      </c>
+      <c r="G14" s="13">
+        <v>455364</v>
+      </c>
+      <c r="H14" s="13">
+        <v>509940</v>
+      </c>
+      <c r="I14" s="13">
+        <v>305964</v>
+      </c>
+      <c r="J14" s="13">
+        <v>509940</v>
+      </c>
+      <c r="K14" s="13">
+        <v>305964</v>
+      </c>
+      <c r="L14" s="13">
+        <v>0</v>
+      </c>
+      <c r="M14" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A15" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="13">
+        <v>100</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="13">
+        <v>324000</v>
+      </c>
+      <c r="F15" s="13">
+        <v>79500</v>
+      </c>
+      <c r="G15" s="13">
+        <v>79500</v>
+      </c>
+      <c r="H15" s="13">
+        <v>27500</v>
+      </c>
+      <c r="I15" s="13">
+        <v>27500</v>
+      </c>
+      <c r="J15" s="13">
+        <v>27500</v>
+      </c>
+      <c r="K15" s="13">
+        <v>27500</v>
+      </c>
+      <c r="L15" s="13">
+        <v>27500</v>
+      </c>
+      <c r="M15" s="13">
+        <v>27500</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="O18" s="11"/>
+      <c r="P18" s="11"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="11"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="O20" s="11"/>
+      <c r="P20" s="11"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="11"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="O22" s="11"/>
+      <c r="P22" s="11"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="O23" s="11"/>
+      <c r="P23" s="11"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="O24" s="11"/>
+      <c r="P24" s="11"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="11"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="O26" s="11"/>
+      <c r="P26" s="11"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="O27" s="11"/>
+      <c r="P27" s="11"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="O28" s="11"/>
+      <c r="P28" s="11"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="O29" s="11"/>
+      <c r="P29" s="11"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="O30" s="11"/>
+      <c r="P30" s="11"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB00D621-D09E-4E2A-8074-2C721C8FF999}">
+  <dimension ref="A1:P32"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="23.125" customWidth="1"/>
+    <col min="3" max="3" width="7.25" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="17.625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
     <col min="7" max="7" width="14.75" customWidth="1"/>
@@ -3226,7 +4312,7 @@
         <v>2422035</v>
       </c>
       <c r="O3" s="1">
-        <f t="shared" ref="O3" si="4">+$C3*N3/100</f>
+        <f t="shared" ref="O3:O15" si="4">+$C3*N3/100</f>
         <v>1089915.75</v>
       </c>
     </row>
@@ -3279,7 +4365,7 @@
         <v>1159450</v>
       </c>
       <c r="O4" s="1">
-        <f t="shared" ref="O4" si="5">+$C4*N4/100</f>
+        <f t="shared" si="4"/>
         <v>579725</v>
       </c>
     </row>
@@ -3332,7 +4418,7 @@
         <v>155370</v>
       </c>
       <c r="O5" s="1">
-        <f t="shared" ref="O5" si="6">+$C5*N5/100</f>
+        <f t="shared" si="4"/>
         <v>77685</v>
       </c>
     </row>
@@ -3385,7 +4471,7 @@
         <v>27000</v>
       </c>
       <c r="O6" s="1">
-        <f t="shared" ref="O6" si="7">+$C6*N6/100</f>
+        <f t="shared" si="4"/>
         <v>13500</v>
       </c>
     </row>
@@ -3438,7 +4524,7 @@
         <v>82500</v>
       </c>
       <c r="O7" s="1">
-        <f t="shared" ref="O7" si="8">+$C7*N7/100</f>
+        <f t="shared" si="4"/>
         <v>49500</v>
       </c>
     </row>
@@ -3491,7 +4577,7 @@
         <v>49000</v>
       </c>
       <c r="O8" s="1">
-        <f t="shared" ref="O8" si="9">+$C8*N8/100</f>
+        <f t="shared" si="4"/>
         <v>24500</v>
       </c>
     </row>
@@ -3544,7 +4630,7 @@
         <v>106000</v>
       </c>
       <c r="O9" s="1">
-        <f t="shared" ref="O9" si="10">+$C9*N9/100</f>
+        <f t="shared" si="4"/>
         <v>106000</v>
       </c>
     </row>
@@ -3597,7 +4683,7 @@
         <v>77000</v>
       </c>
       <c r="O10" s="1">
-        <f t="shared" ref="O10" si="11">+$C10*N10/100</f>
+        <f t="shared" si="4"/>
         <v>38500</v>
       </c>
     </row>
@@ -3650,7 +4736,7 @@
         <v>29100</v>
       </c>
       <c r="O11" s="1">
-        <f t="shared" ref="O11" si="12">+$C11*N11/100</f>
+        <f t="shared" si="4"/>
         <v>11640</v>
       </c>
     </row>
@@ -3703,7 +4789,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="1">
-        <f t="shared" ref="O12" si="13">+$C12*N12/100</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -3756,7 +4842,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="1">
-        <f t="shared" ref="O13" si="14">+$C13*N13/100</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -3809,7 +4895,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="1">
-        <f t="shared" ref="O14" si="15">+$C14*N14/100</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -3862,8 +4948,681 @@
         <v>27500</v>
       </c>
       <c r="O15" s="1">
-        <f t="shared" ref="O15" si="16">+$C15*N15/100</f>
+        <f t="shared" si="4"/>
         <v>27500</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A17" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A18" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="11">
+        <v>40</v>
+      </c>
+      <c r="D18" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="11">
+        <v>664048</v>
+      </c>
+      <c r="F18">
+        <v>118580</v>
+      </c>
+      <c r="G18">
+        <v>47432</v>
+      </c>
+      <c r="H18" s="11">
+        <v>118580</v>
+      </c>
+      <c r="I18" s="11">
+        <v>47432</v>
+      </c>
+      <c r="J18" s="11">
+        <v>118580</v>
+      </c>
+      <c r="K18" s="11">
+        <v>47432</v>
+      </c>
+      <c r="L18" s="11">
+        <v>118580</v>
+      </c>
+      <c r="M18" s="11">
+        <v>47432</v>
+      </c>
+      <c r="O18" s="11"/>
+      <c r="P18" s="11"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A19" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="11">
+        <v>45</v>
+      </c>
+      <c r="D19" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="11">
+        <v>14047572</v>
+      </c>
+      <c r="F19">
+        <v>2422035</v>
+      </c>
+      <c r="G19">
+        <v>1089858</v>
+      </c>
+      <c r="H19" s="11">
+        <v>2422035</v>
+      </c>
+      <c r="I19" s="11">
+        <v>1089858</v>
+      </c>
+      <c r="J19" s="11">
+        <v>2422035</v>
+      </c>
+      <c r="K19" s="11">
+        <v>1089858</v>
+      </c>
+      <c r="L19" s="11">
+        <v>2422035</v>
+      </c>
+      <c r="M19" s="11">
+        <v>1089858</v>
+      </c>
+      <c r="O19" s="11"/>
+      <c r="P19" s="11"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A20" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="11">
+        <v>50</v>
+      </c>
+      <c r="D20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" s="11">
+        <v>6956700</v>
+      </c>
+      <c r="F20">
+        <v>1159450</v>
+      </c>
+      <c r="G20">
+        <v>579725</v>
+      </c>
+      <c r="H20" s="11">
+        <v>1159450</v>
+      </c>
+      <c r="I20" s="11">
+        <v>579725</v>
+      </c>
+      <c r="J20" s="11">
+        <v>1159450</v>
+      </c>
+      <c r="K20" s="11">
+        <v>579725</v>
+      </c>
+      <c r="L20" s="11">
+        <v>1159450</v>
+      </c>
+      <c r="M20" s="11">
+        <v>579725</v>
+      </c>
+      <c r="O20" s="11"/>
+      <c r="P20" s="11"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A21" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="11">
+        <v>50</v>
+      </c>
+      <c r="D21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E21" s="11">
+        <v>932220</v>
+      </c>
+      <c r="F21">
+        <v>155370</v>
+      </c>
+      <c r="G21">
+        <v>77685</v>
+      </c>
+      <c r="H21" s="11">
+        <v>155370</v>
+      </c>
+      <c r="I21" s="11">
+        <v>77685</v>
+      </c>
+      <c r="J21" s="11">
+        <v>155370</v>
+      </c>
+      <c r="K21" s="11">
+        <v>77685</v>
+      </c>
+      <c r="L21" s="11">
+        <v>155370</v>
+      </c>
+      <c r="M21" s="11">
+        <v>77685</v>
+      </c>
+      <c r="O21" s="11"/>
+      <c r="P21" s="11"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A22" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="11">
+        <v>50</v>
+      </c>
+      <c r="D22" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="11">
+        <v>162000</v>
+      </c>
+      <c r="F22">
+        <v>27000</v>
+      </c>
+      <c r="G22">
+        <v>13500</v>
+      </c>
+      <c r="H22" s="11">
+        <v>27000</v>
+      </c>
+      <c r="I22" s="11">
+        <v>13500</v>
+      </c>
+      <c r="J22" s="11">
+        <v>27000</v>
+      </c>
+      <c r="K22" s="11">
+        <v>13500</v>
+      </c>
+      <c r="L22" s="11">
+        <v>27000</v>
+      </c>
+      <c r="M22" s="11">
+        <v>13500</v>
+      </c>
+      <c r="O22" s="11"/>
+      <c r="P22" s="11"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A23" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="11">
+        <v>60</v>
+      </c>
+      <c r="D23" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="11">
+        <v>528000</v>
+      </c>
+      <c r="F23">
+        <v>82500</v>
+      </c>
+      <c r="G23">
+        <v>49500</v>
+      </c>
+      <c r="H23" s="11">
+        <v>82500</v>
+      </c>
+      <c r="I23" s="11">
+        <v>49500</v>
+      </c>
+      <c r="J23" s="11">
+        <v>82500</v>
+      </c>
+      <c r="K23" s="11">
+        <v>49500</v>
+      </c>
+      <c r="L23" s="11">
+        <v>82500</v>
+      </c>
+      <c r="M23" s="11">
+        <v>49500</v>
+      </c>
+      <c r="O23" s="11"/>
+      <c r="P23" s="11"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A24" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="11">
+        <v>50</v>
+      </c>
+      <c r="D24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" s="11">
+        <v>294000</v>
+      </c>
+      <c r="F24">
+        <v>49000</v>
+      </c>
+      <c r="G24">
+        <v>24500</v>
+      </c>
+      <c r="H24" s="11">
+        <v>49000</v>
+      </c>
+      <c r="I24" s="11">
+        <v>24500</v>
+      </c>
+      <c r="J24" s="11">
+        <v>49000</v>
+      </c>
+      <c r="K24" s="11">
+        <v>24500</v>
+      </c>
+      <c r="L24" s="11">
+        <v>49000</v>
+      </c>
+      <c r="M24" s="11">
+        <v>24500</v>
+      </c>
+      <c r="O24" s="11"/>
+      <c r="P24" s="11"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A25" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" s="11">
+        <v>100</v>
+      </c>
+      <c r="D25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" s="11">
+        <v>848000</v>
+      </c>
+      <c r="F25">
+        <v>106000</v>
+      </c>
+      <c r="G25">
+        <v>106000</v>
+      </c>
+      <c r="H25" s="11">
+        <v>106000</v>
+      </c>
+      <c r="I25" s="11">
+        <v>106000</v>
+      </c>
+      <c r="J25" s="11">
+        <v>106000</v>
+      </c>
+      <c r="K25" s="11">
+        <v>106000</v>
+      </c>
+      <c r="L25" s="11">
+        <v>106000</v>
+      </c>
+      <c r="M25" s="11">
+        <v>106000</v>
+      </c>
+      <c r="O25" s="11"/>
+      <c r="P25" s="11"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A26" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="11">
+        <v>50</v>
+      </c>
+      <c r="D26" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26" s="11">
+        <v>462000</v>
+      </c>
+      <c r="F26">
+        <v>77000</v>
+      </c>
+      <c r="G26">
+        <v>38500</v>
+      </c>
+      <c r="H26" s="11">
+        <v>77000</v>
+      </c>
+      <c r="I26" s="11">
+        <v>38500</v>
+      </c>
+      <c r="J26" s="11">
+        <v>77000</v>
+      </c>
+      <c r="K26" s="11">
+        <v>38500</v>
+      </c>
+      <c r="L26" s="11">
+        <v>77000</v>
+      </c>
+      <c r="M26" s="11">
+        <v>38500</v>
+      </c>
+      <c r="O26" s="11"/>
+      <c r="P26" s="11"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A27" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="11">
+        <v>40</v>
+      </c>
+      <c r="D27" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" s="11">
+        <v>162960</v>
+      </c>
+      <c r="F27">
+        <v>29100</v>
+      </c>
+      <c r="G27">
+        <v>11640</v>
+      </c>
+      <c r="H27" s="11">
+        <v>29100</v>
+      </c>
+      <c r="I27" s="11">
+        <v>11640</v>
+      </c>
+      <c r="J27" s="11">
+        <v>29100</v>
+      </c>
+      <c r="K27" s="11">
+        <v>11640</v>
+      </c>
+      <c r="L27" s="11">
+        <v>29100</v>
+      </c>
+      <c r="M27" s="11">
+        <v>11640</v>
+      </c>
+      <c r="O27" s="11"/>
+      <c r="P27" s="11"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A28" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="11">
+        <v>50</v>
+      </c>
+      <c r="D28" t="s">
+        <v>41</v>
+      </c>
+      <c r="E28" s="11">
+        <v>11036031</v>
+      </c>
+      <c r="F28">
+        <v>3781054</v>
+      </c>
+      <c r="G28">
+        <v>1890527</v>
+      </c>
+      <c r="H28" s="11">
+        <v>3576300</v>
+      </c>
+      <c r="I28" s="11">
+        <v>1788150</v>
+      </c>
+      <c r="J28" s="11">
+        <v>0</v>
+      </c>
+      <c r="K28" s="11">
+        <v>0</v>
+      </c>
+      <c r="L28" s="11">
+        <v>0</v>
+      </c>
+      <c r="M28" s="11">
+        <v>0</v>
+      </c>
+      <c r="O28" s="11"/>
+      <c r="P28" s="11"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A29" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" s="11">
+        <v>30</v>
+      </c>
+      <c r="D29" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" s="11">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29" s="11">
+        <v>0</v>
+      </c>
+      <c r="I29" s="11">
+        <v>0</v>
+      </c>
+      <c r="J29" s="11">
+        <v>0</v>
+      </c>
+      <c r="K29" s="11">
+        <v>0</v>
+      </c>
+      <c r="L29" s="11">
+        <v>0</v>
+      </c>
+      <c r="M29" s="11">
+        <v>0</v>
+      </c>
+      <c r="O29" s="11"/>
+      <c r="P29" s="11"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30">
+        <v>60</v>
+      </c>
+      <c r="D30" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30">
+        <v>2846112</v>
+      </c>
+      <c r="F30">
+        <v>758940</v>
+      </c>
+      <c r="G30">
+        <v>455364</v>
+      </c>
+      <c r="H30">
+        <v>509940</v>
+      </c>
+      <c r="I30">
+        <v>305964</v>
+      </c>
+      <c r="J30">
+        <v>509940</v>
+      </c>
+      <c r="K30">
+        <v>305964</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="O30" s="11"/>
+      <c r="P30" s="11"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31">
+        <v>100</v>
+      </c>
+      <c r="D31" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31">
+        <v>324000</v>
+      </c>
+      <c r="F31">
+        <v>79500</v>
+      </c>
+      <c r="G31">
+        <v>79500</v>
+      </c>
+      <c r="H31">
+        <v>27500</v>
+      </c>
+      <c r="I31">
+        <v>27500</v>
+      </c>
+      <c r="J31">
+        <v>27500</v>
+      </c>
+      <c r="K31">
+        <v>27500</v>
+      </c>
+      <c r="L31">
+        <v>27500</v>
+      </c>
+      <c r="M31">
+        <v>27500</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>38</v>
+      </c>
+      <c r="E32">
+        <v>39263643</v>
+      </c>
+      <c r="F32">
+        <v>8845529</v>
+      </c>
+      <c r="G32">
+        <v>4463731</v>
+      </c>
+      <c r="H32">
+        <v>8339775</v>
+      </c>
+      <c r="I32">
+        <v>4159954</v>
+      </c>
+      <c r="J32">
+        <v>4763475</v>
+      </c>
+      <c r="K32">
+        <v>2371804</v>
+      </c>
+      <c r="L32">
+        <v>4253535</v>
+      </c>
+      <c r="M32">
+        <v>2065840</v>
       </c>
     </row>
   </sheetData>
@@ -3872,9 +5631,685 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FB0B00-A757-47DA-9639-AAC1025CB859}">
+  <dimension ref="A3:M19"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="35.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="12" width="15" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A3" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A4" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="8">
+        <v>40</v>
+      </c>
+      <c r="D5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="8">
+        <v>118580</v>
+      </c>
+      <c r="F5" s="8">
+        <v>47432</v>
+      </c>
+      <c r="G5" s="8">
+        <v>118580</v>
+      </c>
+      <c r="H5" s="8">
+        <v>47432</v>
+      </c>
+      <c r="I5" s="8">
+        <v>118580</v>
+      </c>
+      <c r="J5" s="8">
+        <v>47432</v>
+      </c>
+      <c r="K5" s="8">
+        <v>118580</v>
+      </c>
+      <c r="L5" s="8">
+        <v>47432</v>
+      </c>
+      <c r="M5" s="8">
+        <v>664048</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="8">
+        <v>45</v>
+      </c>
+      <c r="D6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="8">
+        <v>2422035</v>
+      </c>
+      <c r="F6" s="8">
+        <v>1089858</v>
+      </c>
+      <c r="G6" s="8">
+        <v>2422035</v>
+      </c>
+      <c r="H6" s="8">
+        <v>1089858</v>
+      </c>
+      <c r="I6" s="8">
+        <v>2422035</v>
+      </c>
+      <c r="J6" s="8">
+        <v>1089858</v>
+      </c>
+      <c r="K6" s="8">
+        <v>2422035</v>
+      </c>
+      <c r="L6" s="8">
+        <v>1089858</v>
+      </c>
+      <c r="M6" s="8">
+        <v>14047572</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="8">
+        <v>50</v>
+      </c>
+      <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="8">
+        <v>1159450</v>
+      </c>
+      <c r="F7" s="8">
+        <v>579725</v>
+      </c>
+      <c r="G7" s="8">
+        <v>1159450</v>
+      </c>
+      <c r="H7" s="8">
+        <v>579725</v>
+      </c>
+      <c r="I7" s="8">
+        <v>1159450</v>
+      </c>
+      <c r="J7" s="8">
+        <v>579725</v>
+      </c>
+      <c r="K7" s="8">
+        <v>1159450</v>
+      </c>
+      <c r="L7" s="8">
+        <v>579725</v>
+      </c>
+      <c r="M7" s="8">
+        <v>6956700</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="8">
+        <v>50</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="8">
+        <v>155370</v>
+      </c>
+      <c r="F8" s="8">
+        <v>77685</v>
+      </c>
+      <c r="G8" s="8">
+        <v>155370</v>
+      </c>
+      <c r="H8" s="8">
+        <v>77685</v>
+      </c>
+      <c r="I8" s="8">
+        <v>155370</v>
+      </c>
+      <c r="J8" s="8">
+        <v>77685</v>
+      </c>
+      <c r="K8" s="8">
+        <v>155370</v>
+      </c>
+      <c r="L8" s="8">
+        <v>77685</v>
+      </c>
+      <c r="M8" s="8">
+        <v>932220</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="8">
+        <v>50</v>
+      </c>
+      <c r="D9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="8">
+        <v>27000</v>
+      </c>
+      <c r="F9" s="8">
+        <v>13500</v>
+      </c>
+      <c r="G9" s="8">
+        <v>27000</v>
+      </c>
+      <c r="H9" s="8">
+        <v>13500</v>
+      </c>
+      <c r="I9" s="8">
+        <v>27000</v>
+      </c>
+      <c r="J9" s="8">
+        <v>13500</v>
+      </c>
+      <c r="K9" s="8">
+        <v>27000</v>
+      </c>
+      <c r="L9" s="8">
+        <v>13500</v>
+      </c>
+      <c r="M9" s="8">
+        <v>162000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="8">
+        <v>60</v>
+      </c>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="8">
+        <v>82500</v>
+      </c>
+      <c r="F10" s="8">
+        <v>49500</v>
+      </c>
+      <c r="G10" s="8">
+        <v>82500</v>
+      </c>
+      <c r="H10" s="8">
+        <v>49500</v>
+      </c>
+      <c r="I10" s="8">
+        <v>82500</v>
+      </c>
+      <c r="J10" s="8">
+        <v>49500</v>
+      </c>
+      <c r="K10" s="8">
+        <v>82500</v>
+      </c>
+      <c r="L10" s="8">
+        <v>49500</v>
+      </c>
+      <c r="M10" s="8">
+        <v>528000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="8">
+        <v>50</v>
+      </c>
+      <c r="D11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="8">
+        <v>49000</v>
+      </c>
+      <c r="F11" s="8">
+        <v>24500</v>
+      </c>
+      <c r="G11" s="8">
+        <v>49000</v>
+      </c>
+      <c r="H11" s="8">
+        <v>24500</v>
+      </c>
+      <c r="I11" s="8">
+        <v>49000</v>
+      </c>
+      <c r="J11" s="8">
+        <v>24500</v>
+      </c>
+      <c r="K11" s="8">
+        <v>49000</v>
+      </c>
+      <c r="L11" s="8">
+        <v>24500</v>
+      </c>
+      <c r="M11" s="8">
+        <v>294000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="8">
+        <v>100</v>
+      </c>
+      <c r="D12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="8">
+        <v>106000</v>
+      </c>
+      <c r="F12" s="8">
+        <v>106000</v>
+      </c>
+      <c r="G12" s="8">
+        <v>106000</v>
+      </c>
+      <c r="H12" s="8">
+        <v>106000</v>
+      </c>
+      <c r="I12" s="8">
+        <v>106000</v>
+      </c>
+      <c r="J12" s="8">
+        <v>106000</v>
+      </c>
+      <c r="K12" s="8">
+        <v>106000</v>
+      </c>
+      <c r="L12" s="8">
+        <v>106000</v>
+      </c>
+      <c r="M12" s="8">
+        <v>848000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="8">
+        <v>50</v>
+      </c>
+      <c r="D13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="8">
+        <v>77000</v>
+      </c>
+      <c r="F13" s="8">
+        <v>38500</v>
+      </c>
+      <c r="G13" s="8">
+        <v>77000</v>
+      </c>
+      <c r="H13" s="8">
+        <v>38500</v>
+      </c>
+      <c r="I13" s="8">
+        <v>77000</v>
+      </c>
+      <c r="J13" s="8">
+        <v>38500</v>
+      </c>
+      <c r="K13" s="8">
+        <v>77000</v>
+      </c>
+      <c r="L13" s="8">
+        <v>38500</v>
+      </c>
+      <c r="M13" s="8">
+        <v>462000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="8">
+        <v>40</v>
+      </c>
+      <c r="D14" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="8">
+        <v>29100</v>
+      </c>
+      <c r="F14" s="8">
+        <v>11640</v>
+      </c>
+      <c r="G14" s="8">
+        <v>29100</v>
+      </c>
+      <c r="H14" s="8">
+        <v>11640</v>
+      </c>
+      <c r="I14" s="8">
+        <v>29100</v>
+      </c>
+      <c r="J14" s="8">
+        <v>11640</v>
+      </c>
+      <c r="K14" s="8">
+        <v>29100</v>
+      </c>
+      <c r="L14" s="8">
+        <v>11640</v>
+      </c>
+      <c r="M14" s="8">
+        <v>162960</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="8">
+        <v>50</v>
+      </c>
+      <c r="D15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="8">
+        <v>3781054</v>
+      </c>
+      <c r="F15" s="8">
+        <v>1890527</v>
+      </c>
+      <c r="G15" s="8">
+        <v>3576300</v>
+      </c>
+      <c r="H15" s="8">
+        <v>1788150</v>
+      </c>
+      <c r="I15" s="8">
+        <v>0</v>
+      </c>
+      <c r="J15" s="8">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8">
+        <v>0</v>
+      </c>
+      <c r="L15" s="8">
+        <v>0</v>
+      </c>
+      <c r="M15" s="8">
+        <v>11036031</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="8">
+        <v>30</v>
+      </c>
+      <c r="D16" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0</v>
+      </c>
+      <c r="F16" s="8">
+        <v>0</v>
+      </c>
+      <c r="G16" s="8">
+        <v>0</v>
+      </c>
+      <c r="H16" s="8">
+        <v>0</v>
+      </c>
+      <c r="I16" s="8">
+        <v>0</v>
+      </c>
+      <c r="J16" s="8">
+        <v>0</v>
+      </c>
+      <c r="K16" s="8">
+        <v>0</v>
+      </c>
+      <c r="L16" s="8">
+        <v>0</v>
+      </c>
+      <c r="M16" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="8">
+        <v>60</v>
+      </c>
+      <c r="D17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="8">
+        <v>758940</v>
+      </c>
+      <c r="F17" s="8">
+        <v>455364</v>
+      </c>
+      <c r="G17" s="8">
+        <v>509940</v>
+      </c>
+      <c r="H17" s="8">
+        <v>305964</v>
+      </c>
+      <c r="I17" s="8">
+        <v>509940</v>
+      </c>
+      <c r="J17" s="8">
+        <v>305964</v>
+      </c>
+      <c r="K17" s="8">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8">
+        <v>0</v>
+      </c>
+      <c r="M17" s="8">
+        <v>2846112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="8">
+        <v>100</v>
+      </c>
+      <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" s="8">
+        <v>79500</v>
+      </c>
+      <c r="F18" s="8">
+        <v>79500</v>
+      </c>
+      <c r="G18" s="8">
+        <v>27500</v>
+      </c>
+      <c r="H18" s="8">
+        <v>27500</v>
+      </c>
+      <c r="I18" s="8">
+        <v>27500</v>
+      </c>
+      <c r="J18" s="8">
+        <v>27500</v>
+      </c>
+      <c r="K18" s="8">
+        <v>27500</v>
+      </c>
+      <c r="L18" s="8">
+        <v>27500</v>
+      </c>
+      <c r="M18" s="8">
+        <v>324000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" s="8">
+        <v>8845529</v>
+      </c>
+      <c r="F19" s="8">
+        <v>4463731</v>
+      </c>
+      <c r="G19" s="8">
+        <v>8339775</v>
+      </c>
+      <c r="H19" s="8">
+        <v>4159954</v>
+      </c>
+      <c r="I19" s="8">
+        <v>4763475</v>
+      </c>
+      <c r="J19" s="8">
+        <v>2371804</v>
+      </c>
+      <c r="K19" s="8">
+        <v>4253535</v>
+      </c>
+      <c r="L19" s="8">
+        <v>2065840</v>
+      </c>
+      <c r="M19" s="8">
+        <v>39263643</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{658C8222-73C6-4D7A-9EF3-E6DA4E4D75CF}">
-  <dimension ref="A1:H113"/>
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -4114,7 +6549,7 @@
         <v>17</v>
       </c>
       <c r="F11" s="1">
-        <v>1089915.75</v>
+        <v>1089858</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
@@ -4156,7 +6591,7 @@
         <v>18</v>
       </c>
       <c r="F13" s="1">
-        <v>1089915.75</v>
+        <v>1089858</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.4">
@@ -4198,7 +6633,7 @@
         <v>26</v>
       </c>
       <c r="F15" s="1">
-        <v>1089915.75</v>
+        <v>1089858</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.4">
@@ -4240,7 +6675,7 @@
         <v>19</v>
       </c>
       <c r="F17" s="1">
-        <v>1089915.75</v>
+        <v>1089858</v>
       </c>
       <c r="G17" s="8"/>
     </row>
@@ -4280,7 +6715,7 @@
       <c r="E19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="1">
         <v>579725</v>
       </c>
     </row>
@@ -4320,7 +6755,7 @@
       <c r="E21" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="1">
         <v>579725</v>
       </c>
     </row>
@@ -4360,7 +6795,7 @@
       <c r="E23" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="1">
         <v>579725</v>
       </c>
     </row>
@@ -4400,7 +6835,7 @@
       <c r="E25" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="1">
         <v>579725</v>
       </c>
       <c r="G25" s="8"/>
@@ -5252,7 +7687,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A66" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>12</v>
@@ -5273,7 +7708,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A67" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>12</v>
@@ -5294,7 +7729,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A68" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>12</v>
@@ -5315,7 +7750,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A69" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>12</v>
@@ -5336,7 +7771,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A70" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>12</v>
@@ -5357,7 +7792,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A71" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>12</v>
@@ -5378,7 +7813,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A72" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>12</v>
@@ -5399,7 +7834,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A73" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>12</v>
@@ -5566,7 +8001,7 @@
         <v>29100</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A81" s="1" t="s">
         <v>6</v>
       </c>
@@ -5588,7 +8023,7 @@
       </c>
       <c r="G81" s="8"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A82" s="1" t="s">
         <v>6</v>
       </c>
@@ -5608,11 +8043,8 @@
       <c r="F82" s="1">
         <v>3781054</v>
       </c>
-      <c r="H82" s="1">
-        <v>3781054</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A83" s="1" t="s">
         <v>6</v>
       </c>
@@ -5633,7 +8065,7 @@
         <v>1890527</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A84" s="1" t="s">
         <v>6</v>
       </c>
@@ -5654,7 +8086,7 @@
         <v>3576300</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A85" s="1" t="s">
         <v>6</v>
       </c>
@@ -5675,7 +8107,7 @@
         <v>1788150</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A86" s="1" t="s">
         <v>6</v>
       </c>
@@ -5696,7 +8128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A87" s="1" t="s">
         <v>6</v>
       </c>
@@ -5717,7 +8149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A88" s="1" t="s">
         <v>6</v>
       </c>
@@ -5738,7 +8170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A89" s="1" t="s">
         <v>6</v>
       </c>
@@ -5760,7 +8192,7 @@
       </c>
       <c r="G89" s="8"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A90" s="1" t="s">
         <v>6</v>
       </c>
@@ -5781,7 +8213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A91" s="1" t="s">
         <v>6</v>
       </c>
@@ -5802,7 +8234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A92" s="1" t="s">
         <v>6</v>
       </c>
@@ -5823,7 +8255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A93" s="1" t="s">
         <v>6</v>
       </c>
@@ -5844,7 +8276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A94" s="1" t="s">
         <v>6</v>
       </c>
@@ -5865,7 +8297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A95" s="1" t="s">
         <v>6</v>
       </c>
@@ -5886,7 +8318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A96" s="1" t="s">
         <v>6</v>
       </c>
@@ -6268,13 +8700,5542 @@
       <c r="G113" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F105" xr:uid="{658C8222-73C6-4D7A-9EF3-E6DA4E4D75CF}"/>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1505AD87-3F7C-4423-B5C5-BE673605948F}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
+  <dimension ref="A1:G57"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="2" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1">
+        <v>40</v>
+      </c>
+      <c r="E2" s="1" t="str">
+        <f t="shared" ref="E2:E33" si="0">+D2&amp;"%"</f>
+        <v>40%</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="1">
+        <v>118580</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1">
+        <v>40</v>
+      </c>
+      <c r="E3" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>40%</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="1">
+        <v>118580</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="1">
+        <v>40</v>
+      </c>
+      <c r="E4" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>40%</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="1">
+        <v>118580</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="1">
+        <v>40</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>40%</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="1">
+        <v>118580</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
+        <v>45</v>
+      </c>
+      <c r="E6" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>45%</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="1">
+        <v>2422035</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1">
+        <v>45</v>
+      </c>
+      <c r="E7" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>45%</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2422035</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1">
+        <v>45</v>
+      </c>
+      <c r="E8" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>45%</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="1">
+        <v>2422035</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1">
+        <v>45</v>
+      </c>
+      <c r="E9" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>45%</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="1">
+        <v>2422035</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1">
+        <v>50</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="10">
+        <v>1159450</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1">
+        <v>50</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="10">
+        <v>1159450</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1">
+        <v>50</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="10">
+        <v>1159450</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1">
+        <v>50</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="10">
+        <v>1159450</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="1">
+        <v>50</v>
+      </c>
+      <c r="E14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="1">
+        <v>155370</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="1">
+        <v>50</v>
+      </c>
+      <c r="E15" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="1">
+        <v>155370</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="1">
+        <v>50</v>
+      </c>
+      <c r="E16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" s="1">
+        <v>155370</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="1">
+        <v>50</v>
+      </c>
+      <c r="E17" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" s="1">
+        <v>155370</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="1">
+        <v>50</v>
+      </c>
+      <c r="E18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="1">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="1">
+        <v>50</v>
+      </c>
+      <c r="E19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="1">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="1">
+        <v>50</v>
+      </c>
+      <c r="E20" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" s="1">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="1">
+        <v>50</v>
+      </c>
+      <c r="E21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" s="1">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="1">
+        <v>60</v>
+      </c>
+      <c r="E22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>60%</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="1">
+        <v>82500</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="1">
+        <v>60</v>
+      </c>
+      <c r="E23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>60%</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="1">
+        <v>82500</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="1">
+        <v>60</v>
+      </c>
+      <c r="E24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>60%</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G24" s="1">
+        <v>82500</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="1">
+        <v>60</v>
+      </c>
+      <c r="E25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>60%</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G25" s="1">
+        <v>82500</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="1">
+        <v>50</v>
+      </c>
+      <c r="E26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="1">
+        <v>49000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="1">
+        <v>50</v>
+      </c>
+      <c r="E27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G27" s="1">
+        <v>49000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="1">
+        <v>50</v>
+      </c>
+      <c r="E28" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G28" s="1">
+        <v>49000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="1">
+        <v>50</v>
+      </c>
+      <c r="E29" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G29" s="1">
+        <v>49000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1">
+        <v>100</v>
+      </c>
+      <c r="E30" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>100%</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G30" s="1">
+        <v>106000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1">
+        <v>100</v>
+      </c>
+      <c r="E31" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>100%</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G31" s="1">
+        <v>106000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1">
+        <v>100</v>
+      </c>
+      <c r="E32" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>100%</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" s="1">
+        <v>106000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1">
+        <v>100</v>
+      </c>
+      <c r="E33" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>100%</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G33" s="1">
+        <v>106000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" s="1">
+        <v>50</v>
+      </c>
+      <c r="E34" s="1" t="str">
+        <f t="shared" ref="E34:E57" si="1">+D34&amp;"%"</f>
+        <v>50%</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34" s="1">
+        <v>77000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" s="1">
+        <v>50</v>
+      </c>
+      <c r="E35" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50%</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G35" s="1">
+        <v>77000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" s="1">
+        <v>50</v>
+      </c>
+      <c r="E36" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50%</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G36" s="1">
+        <v>77000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" s="1">
+        <v>50</v>
+      </c>
+      <c r="E37" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50%</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G37" s="1">
+        <v>77000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38" s="1">
+        <v>40</v>
+      </c>
+      <c r="E38" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>40%</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G38" s="1">
+        <v>29100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39" s="1">
+        <v>40</v>
+      </c>
+      <c r="E39" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>40%</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G39" s="1">
+        <v>29100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D40" s="1">
+        <v>40</v>
+      </c>
+      <c r="E40" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>40%</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G40" s="1">
+        <v>29100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D41" s="1">
+        <v>40</v>
+      </c>
+      <c r="E41" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>40%</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G41" s="1">
+        <v>29100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D42" s="1">
+        <v>50</v>
+      </c>
+      <c r="E42" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50%</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G42" s="1">
+        <v>3781054</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D43" s="1">
+        <v>50</v>
+      </c>
+      <c r="E43" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50%</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G43" s="1">
+        <v>3576300</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D44" s="1">
+        <v>50</v>
+      </c>
+      <c r="E44" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50%</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D45" s="1">
+        <v>50</v>
+      </c>
+      <c r="E45" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50%</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A46" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D46" s="1">
+        <v>30</v>
+      </c>
+      <c r="E46" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>30%</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D47" s="1">
+        <v>30</v>
+      </c>
+      <c r="E47" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>30%</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D48" s="1">
+        <v>30</v>
+      </c>
+      <c r="E48" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>30%</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A49" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D49" s="1">
+        <v>30</v>
+      </c>
+      <c r="E49" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>30%</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A50" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D50" s="1">
+        <v>60</v>
+      </c>
+      <c r="E50" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>60%</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G50" s="1">
+        <v>758940</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A51" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D51" s="1">
+        <v>60</v>
+      </c>
+      <c r="E51" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>60%</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G51" s="1">
+        <v>509940</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D52" s="1">
+        <v>60</v>
+      </c>
+      <c r="E52" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>60%</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G52" s="1">
+        <v>509940</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A53" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D53" s="1">
+        <v>60</v>
+      </c>
+      <c r="E53" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>60%</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D54" s="1">
+        <v>100</v>
+      </c>
+      <c r="E54" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>100%</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G54" s="1">
+        <v>79500</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A55" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D55" s="1">
+        <v>100</v>
+      </c>
+      <c r="E55" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>100%</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G55" s="1">
+        <v>27500</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" s="1">
+        <v>100</v>
+      </c>
+      <c r="E56" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>100%</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G56" s="1">
+        <v>27500</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A57" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D57" s="1">
+        <v>100</v>
+      </c>
+      <c r="E57" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>100%</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G57" s="1">
+        <v>27500</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G57" xr:uid="{1505AD87-3F7C-4423-B5C5-BE673605948F}"/>
+  <phoneticPr fontId="18"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41E269A3-90DD-4E3D-8479-1AC47B050740}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
+  <dimension ref="A1:H57"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="2" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1">
+        <v>40</v>
+      </c>
+      <c r="E2" s="1" t="str">
+        <f t="shared" ref="E2:E33" si="0">+D2&amp;"%"</f>
+        <v>40%</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="1">
+        <v>47432</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1">
+        <v>40</v>
+      </c>
+      <c r="E3" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>40%</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="1">
+        <v>47432</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="1">
+        <v>40</v>
+      </c>
+      <c r="E4" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>40%</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="1">
+        <v>47432</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="1">
+        <v>40</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>40%</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="1">
+        <v>47432</v>
+      </c>
+      <c r="H5" s="8"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
+        <v>45</v>
+      </c>
+      <c r="E6" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>45%</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1089858</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1">
+        <v>45</v>
+      </c>
+      <c r="E7" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>45%</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1089858</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1">
+        <v>45</v>
+      </c>
+      <c r="E8" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>45%</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1089858</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1">
+        <v>45</v>
+      </c>
+      <c r="E9" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>45%</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1089858</v>
+      </c>
+      <c r="H9" s="8"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1">
+        <v>50</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="1">
+        <v>579725</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1">
+        <v>50</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="1">
+        <v>579725</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1">
+        <v>50</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="1">
+        <v>579725</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1">
+        <v>50</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="1">
+        <v>579725</v>
+      </c>
+      <c r="H13" s="8"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="1">
+        <v>50</v>
+      </c>
+      <c r="E14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="1">
+        <v>77685</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="1">
+        <v>50</v>
+      </c>
+      <c r="E15" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="1">
+        <v>77685</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="1">
+        <v>50</v>
+      </c>
+      <c r="E16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" s="1">
+        <v>77685</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="1">
+        <v>50</v>
+      </c>
+      <c r="E17" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" s="1">
+        <v>77685</v>
+      </c>
+      <c r="H17" s="8"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="1">
+        <v>50</v>
+      </c>
+      <c r="E18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="1">
+        <v>13500</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="1">
+        <v>50</v>
+      </c>
+      <c r="E19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="1">
+        <v>13500</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="1">
+        <v>50</v>
+      </c>
+      <c r="E20" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" s="1">
+        <v>13500</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="1">
+        <v>50</v>
+      </c>
+      <c r="E21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" s="1">
+        <v>13500</v>
+      </c>
+      <c r="H21" s="8"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="1">
+        <v>60</v>
+      </c>
+      <c r="E22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>60%</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="1">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="1">
+        <v>60</v>
+      </c>
+      <c r="E23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>60%</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="1">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="1">
+        <v>60</v>
+      </c>
+      <c r="E24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>60%</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G24" s="1">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="1">
+        <v>60</v>
+      </c>
+      <c r="E25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>60%</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G25" s="1">
+        <v>49500</v>
+      </c>
+      <c r="H25" s="8"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="1">
+        <v>50</v>
+      </c>
+      <c r="E26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="1">
+        <v>24500</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="1">
+        <v>50</v>
+      </c>
+      <c r="E27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G27" s="1">
+        <v>24500</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="1">
+        <v>50</v>
+      </c>
+      <c r="E28" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G28" s="1">
+        <v>24500</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="1">
+        <v>50</v>
+      </c>
+      <c r="E29" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G29" s="1">
+        <v>24500</v>
+      </c>
+      <c r="H29" s="8"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1">
+        <v>100</v>
+      </c>
+      <c r="E30" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>100%</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G30" s="1">
+        <v>106000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1">
+        <v>100</v>
+      </c>
+      <c r="E31" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>100%</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G31" s="1">
+        <v>106000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1">
+        <v>100</v>
+      </c>
+      <c r="E32" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>100%</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" s="1">
+        <v>106000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1">
+        <v>100</v>
+      </c>
+      <c r="E33" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>100%</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G33" s="1">
+        <v>106000</v>
+      </c>
+      <c r="H33" s="8"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" s="1">
+        <v>50</v>
+      </c>
+      <c r="E34" s="1" t="str">
+        <f t="shared" ref="E34:E57" si="1">+D34&amp;"%"</f>
+        <v>50%</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34" s="1">
+        <v>38500</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" s="1">
+        <v>50</v>
+      </c>
+      <c r="E35" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50%</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G35" s="1">
+        <v>38500</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" s="1">
+        <v>50</v>
+      </c>
+      <c r="E36" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50%</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G36" s="1">
+        <v>38500</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" s="1">
+        <v>50</v>
+      </c>
+      <c r="E37" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50%</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G37" s="1">
+        <v>38500</v>
+      </c>
+      <c r="H37" s="8"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38" s="1">
+        <v>40</v>
+      </c>
+      <c r="E38" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>40%</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G38" s="1">
+        <v>11640</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39" s="1">
+        <v>40</v>
+      </c>
+      <c r="E39" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>40%</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G39" s="1">
+        <v>11640</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D40" s="1">
+        <v>40</v>
+      </c>
+      <c r="E40" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>40%</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G40" s="1">
+        <v>11640</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D41" s="1">
+        <v>40</v>
+      </c>
+      <c r="E41" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>40%</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G41" s="1">
+        <v>11640</v>
+      </c>
+      <c r="H41" s="8"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D42" s="1">
+        <v>50</v>
+      </c>
+      <c r="E42" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50%</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G42" s="1">
+        <v>1890527</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D43" s="1">
+        <v>50</v>
+      </c>
+      <c r="E43" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50%</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G43" s="1">
+        <v>1788150</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D44" s="1">
+        <v>50</v>
+      </c>
+      <c r="E44" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50%</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D45" s="1">
+        <v>50</v>
+      </c>
+      <c r="E45" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50%</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="8"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A46" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D46" s="1">
+        <v>30</v>
+      </c>
+      <c r="E46" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>30%</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D47" s="1">
+        <v>30</v>
+      </c>
+      <c r="E47" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>30%</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D48" s="1">
+        <v>30</v>
+      </c>
+      <c r="E48" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>30%</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A49" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D49" s="1">
+        <v>30</v>
+      </c>
+      <c r="E49" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>30%</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0</v>
+      </c>
+      <c r="H49" s="8"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A50" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D50" s="1">
+        <v>60</v>
+      </c>
+      <c r="E50" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>60%</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G50" s="1">
+        <v>455364</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A51" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D51" s="1">
+        <v>60</v>
+      </c>
+      <c r="E51" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>60%</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G51" s="1">
+        <v>305964</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D52" s="1">
+        <v>60</v>
+      </c>
+      <c r="E52" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>60%</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G52" s="1">
+        <v>305964</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A53" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D53" s="1">
+        <v>60</v>
+      </c>
+      <c r="E53" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>60%</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+      <c r="H53" s="8"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D54" s="1">
+        <v>100</v>
+      </c>
+      <c r="E54" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>100%</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G54" s="1">
+        <v>79500</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A55" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D55" s="1">
+        <v>100</v>
+      </c>
+      <c r="E55" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>100%</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G55" s="1">
+        <v>27500</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" s="1">
+        <v>100</v>
+      </c>
+      <c r="E56" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>100%</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G56" s="1">
+        <v>27500</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A57" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D57" s="1">
+        <v>100</v>
+      </c>
+      <c r="E57" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>100%</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G57" s="1">
+        <v>27500</v>
+      </c>
+      <c r="H57" s="8"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G57" xr:uid="{1505AD87-3F7C-4423-B5C5-BE673605948F}"/>
+  <phoneticPr fontId="18"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46EB30D1-F83A-4008-906C-8B50A24D9748}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
+  <dimension ref="A1:H113"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.75" customWidth="1"/>
+    <col min="3" max="3" width="31.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1">
+        <v>40</v>
+      </c>
+      <c r="E2" s="1" t="str">
+        <f t="shared" ref="E2:E65" si="0">+D2&amp;"%"</f>
+        <v>40%</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="1">
+        <v>118580</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1">
+        <v>40</v>
+      </c>
+      <c r="E3" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>40%</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="1">
+        <v>47432</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="1">
+        <v>40</v>
+      </c>
+      <c r="E4" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>40%</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="1">
+        <v>118580</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="1">
+        <v>40</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>40%</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="1">
+        <v>47432</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1">
+        <v>40</v>
+      </c>
+      <c r="E6" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>40%</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="1">
+        <v>118580</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="1">
+        <v>40</v>
+      </c>
+      <c r="E7" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>40%</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="1">
+        <v>47432</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="1">
+        <v>40</v>
+      </c>
+      <c r="E8" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>40%</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="1">
+        <v>118580</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="1">
+        <v>40</v>
+      </c>
+      <c r="E9" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>40%</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="1">
+        <v>47432</v>
+      </c>
+      <c r="H9" s="8"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1">
+        <v>45</v>
+      </c>
+      <c r="E10" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>45%</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="1">
+        <v>2422035</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1">
+        <v>45</v>
+      </c>
+      <c r="E11" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>45%</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1089858</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1">
+        <v>45</v>
+      </c>
+      <c r="E12" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>45%</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2422035</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1">
+        <v>45</v>
+      </c>
+      <c r="E13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>45%</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1089858</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1">
+        <v>45</v>
+      </c>
+      <c r="E14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>45%</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="1">
+        <v>2422035</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1">
+        <v>45</v>
+      </c>
+      <c r="E15" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>45%</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1089858</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1">
+        <v>45</v>
+      </c>
+      <c r="E16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>45%</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" s="1">
+        <v>2422035</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="1">
+        <v>45</v>
+      </c>
+      <c r="E17" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>45%</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1089858</v>
+      </c>
+      <c r="H17" s="8"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1">
+        <v>50</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="10">
+        <v>1159450</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19" s="1">
+        <v>50</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="1">
+        <v>579725</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D20" s="1">
+        <v>50</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="10">
+        <v>1159450</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D21" s="1">
+        <v>50</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="1">
+        <v>579725</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="1">
+        <v>50</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="10">
+        <v>1159450</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D23" s="1">
+        <v>50</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G23" s="1">
+        <v>579725</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D24" s="1">
+        <v>50</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G24" s="10">
+        <v>1159450</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D25" s="1">
+        <v>50</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G25" s="1">
+        <v>579725</v>
+      </c>
+      <c r="H25" s="8"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="1">
+        <v>50</v>
+      </c>
+      <c r="E26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="1">
+        <v>155370</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="1">
+        <v>50</v>
+      </c>
+      <c r="E27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" s="1">
+        <v>77685</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="1">
+        <v>50</v>
+      </c>
+      <c r="E28" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28" s="1">
+        <v>155370</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="1">
+        <v>50</v>
+      </c>
+      <c r="E29" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G29" s="1">
+        <v>77685</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="1">
+        <v>50</v>
+      </c>
+      <c r="E30" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G30" s="1">
+        <v>155370</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="1">
+        <v>50</v>
+      </c>
+      <c r="E31" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G31" s="1">
+        <v>77685</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="1">
+        <v>50</v>
+      </c>
+      <c r="E32" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G32" s="1">
+        <v>155370</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="1">
+        <v>50</v>
+      </c>
+      <c r="E33" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G33" s="1">
+        <v>77685</v>
+      </c>
+      <c r="H33" s="8"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="1">
+        <v>50</v>
+      </c>
+      <c r="E34" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34" s="1">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="1">
+        <v>50</v>
+      </c>
+      <c r="E35" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G35" s="1">
+        <v>13500</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="1">
+        <v>50</v>
+      </c>
+      <c r="E36" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G36" s="1">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="1">
+        <v>50</v>
+      </c>
+      <c r="E37" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G37" s="1">
+        <v>13500</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A38" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="1">
+        <v>50</v>
+      </c>
+      <c r="E38" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G38" s="1">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="1">
+        <v>50</v>
+      </c>
+      <c r="E39" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G39" s="1">
+        <v>13500</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A40" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="1">
+        <v>50</v>
+      </c>
+      <c r="E40" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G40" s="1">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A41" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="1">
+        <v>50</v>
+      </c>
+      <c r="E41" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G41" s="1">
+        <v>13500</v>
+      </c>
+      <c r="H41" s="8"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A42" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="1">
+        <v>60</v>
+      </c>
+      <c r="E42" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>60%</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G42" s="1">
+        <v>82500</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A43" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" s="1">
+        <v>60</v>
+      </c>
+      <c r="E43" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>60%</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G43" s="1">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A44" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="1">
+        <v>60</v>
+      </c>
+      <c r="E44" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>60%</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G44" s="1">
+        <v>82500</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A45" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" s="1">
+        <v>60</v>
+      </c>
+      <c r="E45" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>60%</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G45" s="1">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A46" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" s="1">
+        <v>60</v>
+      </c>
+      <c r="E46" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>60%</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G46" s="1">
+        <v>82500</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" s="1">
+        <v>60</v>
+      </c>
+      <c r="E47" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>60%</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G47" s="1">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A48" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="1">
+        <v>60</v>
+      </c>
+      <c r="E48" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>60%</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G48" s="1">
+        <v>82500</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A49" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" s="1">
+        <v>60</v>
+      </c>
+      <c r="E49" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>60%</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G49" s="1">
+        <v>49500</v>
+      </c>
+      <c r="H49" s="8"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A50" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" s="1">
+        <v>50</v>
+      </c>
+      <c r="E50" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G50" s="1">
+        <v>49000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A51" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" s="1">
+        <v>50</v>
+      </c>
+      <c r="E51" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G51" s="1">
+        <v>24500</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A52" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" s="1">
+        <v>50</v>
+      </c>
+      <c r="E52" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G52" s="1">
+        <v>49000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A53" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D53" s="1">
+        <v>50</v>
+      </c>
+      <c r="E53" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G53" s="1">
+        <v>24500</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A54" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" s="1">
+        <v>50</v>
+      </c>
+      <c r="E54" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G54" s="1">
+        <v>49000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A55" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" s="1">
+        <v>50</v>
+      </c>
+      <c r="E55" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G55" s="1">
+        <v>24500</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A56" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" s="1">
+        <v>50</v>
+      </c>
+      <c r="E56" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G56" s="1">
+        <v>49000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A57" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" s="1">
+        <v>50</v>
+      </c>
+      <c r="E57" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>50%</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G57" s="1">
+        <v>24500</v>
+      </c>
+      <c r="H57" s="8"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A58" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1">
+        <v>100</v>
+      </c>
+      <c r="E58" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>100%</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G58" s="1">
+        <v>106000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A59" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" s="1">
+        <v>100</v>
+      </c>
+      <c r="E59" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>100%</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G59" s="1">
+        <v>106000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A60" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D60" s="1">
+        <v>100</v>
+      </c>
+      <c r="E60" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>100%</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G60" s="1">
+        <v>106000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A61" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" s="1">
+        <v>100</v>
+      </c>
+      <c r="E61" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>100%</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G61" s="1">
+        <v>106000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A62" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1">
+        <v>100</v>
+      </c>
+      <c r="E62" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>100%</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G62" s="1">
+        <v>106000</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A63" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D63" s="1">
+        <v>100</v>
+      </c>
+      <c r="E63" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>100%</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G63" s="1">
+        <v>106000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A64" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D64" s="1">
+        <v>100</v>
+      </c>
+      <c r="E64" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>100%</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G64" s="1">
+        <v>106000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A65" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D65" s="1">
+        <v>100</v>
+      </c>
+      <c r="E65" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>100%</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G65" s="1">
+        <v>106000</v>
+      </c>
+      <c r="H65" s="8"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A66" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D66" s="1">
+        <v>50</v>
+      </c>
+      <c r="E66" s="1" t="str">
+        <f t="shared" ref="E66:E113" si="1">+D66&amp;"%"</f>
+        <v>50%</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G66" s="1">
+        <v>77000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A67" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D67" s="1">
+        <v>50</v>
+      </c>
+      <c r="E67" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50%</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G67" s="1">
+        <v>38500</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A68" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D68" s="1">
+        <v>50</v>
+      </c>
+      <c r="E68" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50%</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G68" s="1">
+        <v>77000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A69" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D69" s="1">
+        <v>50</v>
+      </c>
+      <c r="E69" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50%</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G69" s="1">
+        <v>38500</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A70" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D70" s="1">
+        <v>50</v>
+      </c>
+      <c r="E70" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50%</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G70" s="1">
+        <v>77000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A71" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D71" s="1">
+        <v>50</v>
+      </c>
+      <c r="E71" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50%</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G71" s="1">
+        <v>38500</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A72" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D72" s="1">
+        <v>50</v>
+      </c>
+      <c r="E72" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50%</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G72" s="1">
+        <v>77000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A73" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D73" s="1">
+        <v>50</v>
+      </c>
+      <c r="E73" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50%</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G73" s="1">
+        <v>38500</v>
+      </c>
+      <c r="H73" s="8"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A74" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D74" s="1">
+        <v>40</v>
+      </c>
+      <c r="E74" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>40%</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G74" s="1">
+        <v>29100</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A75" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D75" s="1">
+        <v>40</v>
+      </c>
+      <c r="E75" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>40%</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G75" s="1">
+        <v>11640</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A76" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D76" s="1">
+        <v>40</v>
+      </c>
+      <c r="E76" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>40%</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G76" s="1">
+        <v>29100</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A77" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D77" s="1">
+        <v>40</v>
+      </c>
+      <c r="E77" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>40%</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G77" s="1">
+        <v>11640</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A78" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D78" s="1">
+        <v>40</v>
+      </c>
+      <c r="E78" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>40%</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G78" s="1">
+        <v>29100</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A79" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D79" s="1">
+        <v>40</v>
+      </c>
+      <c r="E79" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>40%</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G79" s="1">
+        <v>11640</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A80" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D80" s="1">
+        <v>40</v>
+      </c>
+      <c r="E80" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>40%</v>
+      </c>
+      <c r="F80" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G80" s="1">
+        <v>29100</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A81" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D81" s="1">
+        <v>40</v>
+      </c>
+      <c r="E81" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>40%</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G81" s="1">
+        <v>11640</v>
+      </c>
+      <c r="H81" s="8"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A82" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D82" s="1">
+        <v>50</v>
+      </c>
+      <c r="E82" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50%</v>
+      </c>
+      <c r="F82" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G82" s="1">
+        <v>3781054</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A83" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D83" s="1">
+        <v>50</v>
+      </c>
+      <c r="E83" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50%</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G83" s="1">
+        <v>1890527</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D84" s="1">
+        <v>50</v>
+      </c>
+      <c r="E84" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50%</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G84" s="1">
+        <v>3576300</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A85" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D85" s="1">
+        <v>50</v>
+      </c>
+      <c r="E85" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50%</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G85" s="1">
+        <v>1788150</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A86" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D86" s="1">
+        <v>50</v>
+      </c>
+      <c r="E86" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50%</v>
+      </c>
+      <c r="F86" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G86" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A87" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D87" s="1">
+        <v>50</v>
+      </c>
+      <c r="E87" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50%</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G87" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A88" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D88" s="1">
+        <v>50</v>
+      </c>
+      <c r="E88" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50%</v>
+      </c>
+      <c r="F88" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G88" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A89" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D89" s="1">
+        <v>50</v>
+      </c>
+      <c r="E89" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50%</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G89" s="1">
+        <v>0</v>
+      </c>
+      <c r="H89" s="8"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A90" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D90" s="1">
+        <v>30</v>
+      </c>
+      <c r="E90" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>30%</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G90" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A91" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D91" s="1">
+        <v>30</v>
+      </c>
+      <c r="E91" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>30%</v>
+      </c>
+      <c r="F91" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G91" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A92" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D92" s="1">
+        <v>30</v>
+      </c>
+      <c r="E92" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>30%</v>
+      </c>
+      <c r="F92" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G92" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A93" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D93" s="1">
+        <v>30</v>
+      </c>
+      <c r="E93" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>30%</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G93" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A94" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D94" s="1">
+        <v>30</v>
+      </c>
+      <c r="E94" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>30%</v>
+      </c>
+      <c r="F94" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G94" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A95" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D95" s="1">
+        <v>30</v>
+      </c>
+      <c r="E95" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>30%</v>
+      </c>
+      <c r="F95" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G95" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A96" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D96" s="1">
+        <v>30</v>
+      </c>
+      <c r="E96" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>30%</v>
+      </c>
+      <c r="F96" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G96" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A97" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D97" s="1">
+        <v>30</v>
+      </c>
+      <c r="E97" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>30%</v>
+      </c>
+      <c r="F97" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G97" s="1">
+        <v>0</v>
+      </c>
+      <c r="H97" s="8"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A98" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D98" s="1">
+        <v>60</v>
+      </c>
+      <c r="E98" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>60%</v>
+      </c>
+      <c r="F98" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G98" s="1">
+        <v>758940</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A99" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D99" s="1">
+        <v>60</v>
+      </c>
+      <c r="E99" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>60%</v>
+      </c>
+      <c r="F99" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G99" s="1">
+        <v>455364</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A100" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D100" s="1">
+        <v>60</v>
+      </c>
+      <c r="E100" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>60%</v>
+      </c>
+      <c r="F100" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G100" s="1">
+        <v>509940</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A101" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D101" s="1">
+        <v>60</v>
+      </c>
+      <c r="E101" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>60%</v>
+      </c>
+      <c r="F101" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G101" s="1">
+        <v>305964</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A102" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D102" s="1">
+        <v>60</v>
+      </c>
+      <c r="E102" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>60%</v>
+      </c>
+      <c r="F102" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G102" s="1">
+        <v>509940</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A103" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D103" s="1">
+        <v>60</v>
+      </c>
+      <c r="E103" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>60%</v>
+      </c>
+      <c r="F103" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G103" s="1">
+        <v>305964</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A104" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D104" s="1">
+        <v>60</v>
+      </c>
+      <c r="E104" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>60%</v>
+      </c>
+      <c r="F104" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G104" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A105" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D105" s="1">
+        <v>60</v>
+      </c>
+      <c r="E105" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>60%</v>
+      </c>
+      <c r="F105" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G105" s="1">
+        <v>0</v>
+      </c>
+      <c r="H105" s="8"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A106" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D106" s="1">
+        <v>100</v>
+      </c>
+      <c r="E106" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>100%</v>
+      </c>
+      <c r="F106" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G106" s="1">
+        <v>79500</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A107" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D107" s="1">
+        <v>100</v>
+      </c>
+      <c r="E107" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>100%</v>
+      </c>
+      <c r="F107" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G107" s="1">
+        <v>79500</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A108" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1">
+        <v>100</v>
+      </c>
+      <c r="E108" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>100%</v>
+      </c>
+      <c r="F108" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G108" s="1">
+        <v>27500</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A109" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1">
+        <v>100</v>
+      </c>
+      <c r="E109" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>100%</v>
+      </c>
+      <c r="F109" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G109" s="1">
+        <v>27500</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A110" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D110" s="1">
+        <v>100</v>
+      </c>
+      <c r="E110" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>100%</v>
+      </c>
+      <c r="F110" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G110" s="1">
+        <v>27500</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A111" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D111" s="1">
+        <v>100</v>
+      </c>
+      <c r="E111" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>100%</v>
+      </c>
+      <c r="F111" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G111" s="1">
+        <v>27500</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A112" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D112" s="1">
+        <v>100</v>
+      </c>
+      <c r="E112" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>100%</v>
+      </c>
+      <c r="F112" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G112" s="1">
+        <v>27500</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A113" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D113" s="1">
+        <v>100</v>
+      </c>
+      <c r="E113" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>100%</v>
+      </c>
+      <c r="F113" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G113" s="1">
+        <v>27500</v>
+      </c>
+      <c r="H113" s="8"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G113" xr:uid="{46EB30D1-F83A-4008-906C-8B50A24D9748}"/>
+  <phoneticPr fontId="18"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD444C4-E2DB-41DD-9EF8-2FA32900CA7C}">
   <dimension ref="A3:K48"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -6376,28 +14337,28 @@
         <v>2422035</v>
       </c>
       <c r="D6" s="8">
-        <v>1089915.75</v>
+        <v>1089858</v>
       </c>
       <c r="E6" s="8">
         <v>2422035</v>
       </c>
       <c r="F6" s="8">
-        <v>1089915.75</v>
+        <v>1089858</v>
       </c>
       <c r="G6" s="8">
         <v>2422035</v>
       </c>
       <c r="H6" s="8">
-        <v>1089915.75</v>
+        <v>1089858</v>
       </c>
       <c r="I6" s="8">
         <v>2422035</v>
       </c>
       <c r="J6" s="8">
-        <v>1089915.75</v>
+        <v>1089858</v>
       </c>
       <c r="K6" s="8">
-        <v>14047803</v>
+        <v>14047572</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.4">
@@ -6720,28 +14681,28 @@
         <v>8845529</v>
       </c>
       <c r="D16" s="8">
-        <v>4463788.75</v>
+        <v>4463731</v>
       </c>
       <c r="E16" s="8">
         <v>8339775</v>
       </c>
       <c r="F16" s="8">
-        <v>4160011.75</v>
+        <v>4159954</v>
       </c>
       <c r="G16" s="8">
         <v>4763475</v>
       </c>
       <c r="H16" s="8">
-        <v>2371861.75</v>
+        <v>2371804</v>
       </c>
       <c r="I16" s="8">
         <v>4253535</v>
       </c>
       <c r="J16" s="8">
-        <v>2065897.75</v>
+        <v>2065840</v>
       </c>
       <c r="K16" s="8">
-        <v>39263874</v>
+        <v>39263643</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.4">
@@ -7313,7 +15274,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14027FC9-3372-4CBC-B2AB-B8693957732A}">
   <dimension ref="A3:M18"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>

--- a/月額_分割統合.xlsx
+++ b/月額_分割統合.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\offic\python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D79205A-1352-48FD-A0D2-5072EB6BFDC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5DF1CD0-BE28-4BFC-AA69-3BB806B0F603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2790" yWindow="1050" windowWidth="23895" windowHeight="13830" activeTab="6" xr2:uid="{5AA50BA7-59BB-4F8D-9D40-E32F9614EBD2}"/>
+    <workbookView xWindow="4245" yWindow="1095" windowWidth="23895" windowHeight="13830" activeTab="6" xr2:uid="{5AA50BA7-59BB-4F8D-9D40-E32F9614EBD2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1676" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1676" uniqueCount="66">
   <si>
     <t>新 業務提携者（従属）</t>
   </si>
@@ -333,6 +333,16 @@
     <t>自社分</t>
     <rPh sb="0" eb="3">
       <t>ジシャブン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>全体売上</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ウリアゲ</t>
     </rPh>
     <phoneticPr fontId="18"/>
   </si>
@@ -11539,7 +11549,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -11587,7 +11597,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
@@ -11635,7 +11645,7 @@
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
@@ -11683,7 +11693,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>5</v>
@@ -11732,7 +11742,7 @@
         <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>1</v>
@@ -11780,7 +11790,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>1</v>
@@ -11828,7 +11838,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>1</v>
@@ -11876,7 +11886,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>1</v>
@@ -11925,7 +11935,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>1</v>
@@ -11971,7 +11981,7 @@
         <v>13</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>1</v>
@@ -12017,7 +12027,7 @@
         <v>13</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>1</v>
@@ -12063,7 +12073,7 @@
         <v>13</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>1</v>
@@ -12110,7 +12120,7 @@
         <v>13</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>8</v>
@@ -12158,7 +12168,7 @@
         <v>13</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>8</v>
@@ -12206,7 +12216,7 @@
         <v>13</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>8</v>
@@ -12254,7 +12264,7 @@
         <v>13</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>8</v>
@@ -12303,7 +12313,7 @@
         <v>13</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>9</v>
@@ -12351,7 +12361,7 @@
         <v>13</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>9</v>
@@ -12399,7 +12409,7 @@
         <v>13</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>9</v>
@@ -12447,7 +12457,7 @@
         <v>13</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>9</v>
@@ -12496,7 +12506,7 @@
         <v>13</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>10</v>
@@ -12544,7 +12554,7 @@
         <v>13</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>10</v>
@@ -12592,7 +12602,7 @@
         <v>13</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>10</v>
@@ -12640,7 +12650,7 @@
         <v>13</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>10</v>
@@ -12689,7 +12699,7 @@
         <v>13</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>11</v>
@@ -12737,7 +12747,7 @@
         <v>13</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>11</v>
@@ -12785,7 +12795,7 @@
         <v>13</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>11</v>
@@ -12833,7 +12843,7 @@
         <v>13</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>11</v>
@@ -12882,7 +12892,7 @@
         <v>13</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -12930,7 +12940,7 @@
         <v>13</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -12978,7 +12988,7 @@
         <v>13</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -13026,7 +13036,7 @@
         <v>13</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -13075,7 +13085,7 @@
         <v>13</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>12</v>
@@ -13123,7 +13133,7 @@
         <v>13</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>12</v>
@@ -13171,7 +13181,7 @@
         <v>13</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>12</v>
@@ -13219,7 +13229,7 @@
         <v>13</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>12</v>
@@ -13268,7 +13278,7 @@
         <v>6</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>5</v>
@@ -13316,7 +13326,7 @@
         <v>6</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>5</v>
@@ -13364,7 +13374,7 @@
         <v>6</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>5</v>
@@ -13412,7 +13422,7 @@
         <v>6</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>5</v>
@@ -13461,7 +13471,7 @@
         <v>6</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>1</v>
@@ -13509,7 +13519,7 @@
         <v>6</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>1</v>
@@ -13557,7 +13567,7 @@
         <v>6</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>1</v>
@@ -13605,7 +13615,7 @@
         <v>6</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>1</v>
@@ -13654,7 +13664,7 @@
         <v>6</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>4</v>
@@ -13702,7 +13712,7 @@
         <v>6</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>4</v>
@@ -13750,7 +13760,7 @@
         <v>6</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>4</v>
@@ -13798,7 +13808,7 @@
         <v>6</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>4</v>
@@ -13847,7 +13857,7 @@
         <v>6</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>2</v>
@@ -13895,7 +13905,7 @@
         <v>6</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>2</v>
@@ -13943,7 +13953,7 @@
         <v>6</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>2</v>
@@ -13991,7 +14001,7 @@
         <v>6</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>2</v>
@@ -14040,7 +14050,7 @@
         <v>6</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
@@ -14088,7 +14098,7 @@
         <v>6</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -14136,7 +14146,7 @@
         <v>6</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
@@ -14184,7 +14194,7 @@
         <v>6</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
